--- a/input/risk/file1_Risk_Input.xlsx
+++ b/input/risk/file1_Risk_Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tolia\Desktop\AI Projects\work stuff\claude version\input\risk raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tolia\Desktop\AI Projects\Claude projects all\Claude projects v3\Project\input\risk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14856416-3D67-4C2A-916A-841BB337FFD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B434DF-57E6-4220-B7E7-0494AB321113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Risk_Main" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="47">
   <si>
     <t>Broker</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>anatoly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDI </t>
   </si>
 </sst>
 </file>
@@ -459,6 +462,11 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="B4" t="s">
+        <v>46</v>
+      </c>
+    </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="1" t="s">
         <v>6</v>
